--- a/app/gpl_audit/GPL.xlsx
+++ b/app/gpl_audit/GPL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aj_mac/Documents/Atel/code/app/gpl_audit/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aj_mac/Documents/Atel/server/code/app/gpl_audit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E105EAC-5E08-4F4E-B2A8-612EDF6A4A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF51A02-A98D-2141-AF9C-9A81EEB89572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16120" activeTab="5" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2751" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3001" uniqueCount="529">
   <si>
     <t>5qi1</t>
   </si>
@@ -1623,6 +1623,12 @@
   </si>
   <si>
     <t>zzzTemporary1</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -5448,7 +5454,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04129BFA-1C57-4A9F-9E8B-6ECAA0BFBBBF}">
-  <dimension ref="A1:I297"/>
+  <dimension ref="A1:I295"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -5511,7 +5517,9 @@
       <c r="F2" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
@@ -5538,7 +5546,9 @@
       <c r="F3" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H3" s="3" t="s">
         <v>17</v>
       </c>
@@ -5565,7 +5575,9 @@
       <c r="F4" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
@@ -5590,7 +5602,9 @@
       <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
@@ -5615,7 +5629,9 @@
       <c r="F6" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H6" s="3" t="s">
         <v>17</v>
       </c>
@@ -5640,7 +5656,9 @@
       <c r="F7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
       </c>
@@ -5665,7 +5683,9 @@
       <c r="F8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H8" s="3" t="s">
         <v>17</v>
       </c>
@@ -5690,7 +5710,9 @@
       <c r="F9" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H9" s="3" t="s">
         <v>17</v>
       </c>
@@ -5715,7 +5737,9 @@
       <c r="F10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H10" s="3" t="s">
         <v>17</v>
       </c>
@@ -5740,7 +5764,9 @@
       <c r="F11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H11" s="3" t="s">
         <v>17</v>
       </c>
@@ -5765,7 +5791,9 @@
       <c r="F12" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H12" s="3" t="s">
         <v>17</v>
       </c>
@@ -5790,7 +5818,9 @@
       <c r="F13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H13" s="3" t="s">
         <v>17</v>
       </c>
@@ -5815,7 +5845,9 @@
       <c r="F14" s="3">
         <v>34</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
@@ -5840,7 +5872,9 @@
       <c r="F15" s="3">
         <v>34</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H15" s="3" t="s">
         <v>17</v>
       </c>
@@ -5865,7 +5899,9 @@
       <c r="F16" s="3">
         <v>12</v>
       </c>
-      <c r="G16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H16" s="3" t="s">
         <v>17</v>
       </c>
@@ -5890,7 +5926,9 @@
       <c r="F17" s="3">
         <v>12</v>
       </c>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H17" s="3" t="s">
         <v>17</v>
       </c>
@@ -5915,7 +5953,9 @@
       <c r="F18" s="3">
         <v>46</v>
       </c>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H18" s="3" t="s">
         <v>17</v>
       </c>
@@ -5940,7 +5980,9 @@
       <c r="F19" s="3">
         <v>32</v>
       </c>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H19" s="3" t="s">
         <v>17</v>
       </c>
@@ -5965,7 +6007,9 @@
       <c r="F20" s="3">
         <v>40</v>
       </c>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H20" s="3" t="s">
         <v>17</v>
       </c>
@@ -5990,7 +6034,9 @@
       <c r="F21" s="3">
         <v>30</v>
       </c>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H21" s="3" t="s">
         <v>17</v>
       </c>
@@ -6015,7 +6061,9 @@
       <c r="F22" s="3">
         <v>26</v>
       </c>
-      <c r="G22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H22" s="3" t="s">
         <v>17</v>
       </c>
@@ -6040,7 +6088,9 @@
       <c r="F23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H23" s="3" t="s">
         <v>17</v>
       </c>
@@ -6065,7 +6115,9 @@
       <c r="F24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G24" s="3"/>
+      <c r="G24" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H24" s="3" t="s">
         <v>17</v>
       </c>
@@ -6090,7 +6142,9 @@
       <c r="F25" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H25" s="3" t="s">
         <v>17</v>
       </c>
@@ -6115,7 +6169,9 @@
       <c r="F26" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H26" s="3" t="s">
         <v>17</v>
       </c>
@@ -6140,7 +6196,9 @@
       <c r="F27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H27" s="3" t="s">
         <v>17</v>
       </c>
@@ -6165,7 +6223,9 @@
       <c r="F28" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="G28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H28" s="3" t="s">
         <v>17</v>
       </c>
@@ -6190,7 +6250,9 @@
       <c r="F29" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H29" s="3" t="s">
         <v>17</v>
       </c>
@@ -6215,7 +6277,9 @@
       <c r="F30" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H30" s="3" t="s">
         <v>17</v>
       </c>
@@ -6240,7 +6304,9 @@
       <c r="F31" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H31" s="3" t="s">
         <v>17</v>
       </c>
@@ -6265,7 +6331,9 @@
       <c r="F32" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H32" s="3" t="s">
         <v>17</v>
       </c>
@@ -6290,7 +6358,9 @@
       <c r="F33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H33" s="3" t="s">
         <v>17</v>
       </c>
@@ -6315,7 +6385,9 @@
       <c r="F34" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="G34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H34" s="3" t="s">
         <v>17</v>
       </c>
@@ -6340,7 +6412,9 @@
       <c r="F35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H35" s="3" t="s">
         <v>17</v>
       </c>
@@ -6365,7 +6439,9 @@
       <c r="F36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H36" s="3" t="s">
         <v>17</v>
       </c>
@@ -6390,7 +6466,9 @@
       <c r="F37" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H37" s="3" t="s">
         <v>17</v>
       </c>
@@ -6415,7 +6493,9 @@
       <c r="F38" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H38" s="3" t="s">
         <v>17</v>
       </c>
@@ -6440,7 +6520,9 @@
       <c r="F39" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G39" s="3"/>
+      <c r="G39" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H39" s="3" t="s">
         <v>17</v>
       </c>
@@ -6465,7 +6547,9 @@
       <c r="F40" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G40" s="3"/>
+      <c r="G40" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H40" s="3" t="s">
         <v>17</v>
       </c>
@@ -6490,7 +6574,9 @@
       <c r="F41" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H41" s="3" t="s">
         <v>17</v>
       </c>
@@ -6515,7 +6601,9 @@
       <c r="F42" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="G42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H42" s="3" t="s">
         <v>17</v>
       </c>
@@ -6540,7 +6628,9 @@
       <c r="F43" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H43" s="3" t="s">
         <v>17</v>
       </c>
@@ -6565,7 +6655,9 @@
       <c r="F44" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H44" s="3" t="s">
         <v>17</v>
       </c>
@@ -6590,7 +6682,9 @@
       <c r="F45" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G45" s="3"/>
+      <c r="G45" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H45" s="3" t="s">
         <v>17</v>
       </c>
@@ -6615,7 +6709,9 @@
       <c r="F46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G46" s="3"/>
+      <c r="G46" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H46" s="3" t="s">
         <v>17</v>
       </c>
@@ -6640,7 +6736,9 @@
       <c r="F47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="3"/>
+      <c r="G47" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H47" s="3" t="s">
         <v>17</v>
       </c>
@@ -6665,7 +6763,9 @@
       <c r="F48" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="G48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H48" s="3" t="s">
         <v>17</v>
       </c>
@@ -6690,7 +6790,9 @@
       <c r="F49" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G49" s="3"/>
+      <c r="G49" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H49" s="3" t="s">
         <v>17</v>
       </c>
@@ -6715,7 +6817,9 @@
       <c r="F50" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="G50" s="3"/>
+      <c r="G50" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H50" s="3" t="s">
         <v>17</v>
       </c>
@@ -6740,7 +6844,9 @@
       <c r="F51" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="G51" s="3"/>
+      <c r="G51" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H51" s="3" t="s">
         <v>17</v>
       </c>
@@ -6765,7 +6871,9 @@
       <c r="F52" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G52" s="3"/>
+      <c r="G52" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H52" s="3" t="s">
         <v>17</v>
       </c>
@@ -6790,7 +6898,9 @@
       <c r="F53" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="G53" s="3"/>
+      <c r="G53" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H53" s="3" t="s">
         <v>17</v>
       </c>
@@ -6815,7 +6925,9 @@
       <c r="F54" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="G54" s="3"/>
+      <c r="G54" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H54" s="3" t="s">
         <v>17</v>
       </c>
@@ -6840,7 +6952,9 @@
       <c r="F55" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G55" s="3"/>
+      <c r="G55" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H55" s="3" t="s">
         <v>17</v>
       </c>
@@ -6865,7 +6979,9 @@
       <c r="F56" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H56" s="3" t="s">
         <v>17</v>
       </c>
@@ -6890,7 +7006,9 @@
       <c r="F57" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G57" s="3"/>
+      <c r="G57" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H57" s="3" t="s">
         <v>17</v>
       </c>
@@ -6915,7 +7033,9 @@
       <c r="F58" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G58" s="3"/>
+      <c r="G58" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H58" s="3" t="s">
         <v>17</v>
       </c>
@@ -6940,7 +7060,9 @@
       <c r="F59" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G59" s="3"/>
+      <c r="G59" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H59" s="3" t="s">
         <v>17</v>
       </c>
@@ -6965,7 +7087,9 @@
       <c r="F60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="3"/>
+      <c r="G60" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H60" s="3" t="s">
         <v>17</v>
       </c>
@@ -6990,7 +7114,9 @@
       <c r="F61" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="G61" s="3"/>
+      <c r="G61" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H61" s="3" t="s">
         <v>17</v>
       </c>
@@ -7015,7 +7141,9 @@
       <c r="F62" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G62" s="3"/>
+      <c r="G62" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H62" s="3" t="s">
         <v>17</v>
       </c>
@@ -7040,7 +7168,9 @@
       <c r="F63" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G63" s="3"/>
+      <c r="G63" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H63" s="3" t="s">
         <v>17</v>
       </c>
@@ -7065,7 +7195,9 @@
       <c r="F64" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G64" s="3"/>
+      <c r="G64" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H64" s="3" t="s">
         <v>17</v>
       </c>
@@ -7087,8 +7219,12 @@
       <c r="E65" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H65" s="3" t="s">
         <v>17</v>
       </c>
@@ -7113,7 +7249,9 @@
       <c r="F66" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="G66" s="3"/>
+      <c r="G66" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H66" s="3" t="s">
         <v>17</v>
       </c>
@@ -7138,7 +7276,9 @@
       <c r="F67" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G67" s="3"/>
+      <c r="G67" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H67" s="3" t="s">
         <v>17</v>
       </c>
@@ -7163,7 +7303,9 @@
       <c r="F68" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G68" s="3"/>
+      <c r="G68" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H68" s="3" t="s">
         <v>17</v>
       </c>
@@ -7188,7 +7330,9 @@
       <c r="F69" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G69" s="3"/>
+      <c r="G69" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H69" s="3" t="s">
         <v>17</v>
       </c>
@@ -7213,7 +7357,9 @@
       <c r="F70" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="G70" s="3"/>
+      <c r="G70" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H70" s="3" t="s">
         <v>17</v>
       </c>
@@ -7238,7 +7384,9 @@
       <c r="F71" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="G71" s="3"/>
+      <c r="G71" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H71" s="3" t="s">
         <v>17</v>
       </c>
@@ -7263,7 +7411,9 @@
       <c r="F72" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="G72" s="3"/>
+      <c r="G72" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H72" s="3" t="s">
         <v>17</v>
       </c>
@@ -7288,7 +7438,9 @@
       <c r="F73" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="G73" s="3"/>
+      <c r="G73" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H73" s="3" t="s">
         <v>17</v>
       </c>
@@ -7313,7 +7465,9 @@
       <c r="F74" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G74" s="3"/>
+      <c r="G74" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H74" s="3" t="s">
         <v>17</v>
       </c>
@@ -7338,7 +7492,9 @@
       <c r="F75" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H75" s="3" t="s">
         <v>17</v>
       </c>
@@ -7363,7 +7519,9 @@
       <c r="F76" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H76" s="3" t="s">
         <v>17</v>
       </c>
@@ -7388,7 +7546,9 @@
       <c r="F77" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H77" s="3" t="s">
         <v>17</v>
       </c>
@@ -7413,7 +7573,9 @@
       <c r="F78" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H78" s="3" t="s">
         <v>17</v>
       </c>
@@ -7438,7 +7600,9 @@
       <c r="F79" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="G79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H79" s="3" t="s">
         <v>17</v>
       </c>
@@ -7463,7 +7627,9 @@
       <c r="F80" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="G80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H80" s="3" t="s">
         <v>17</v>
       </c>
@@ -7488,7 +7654,9 @@
       <c r="F81" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="G81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H81" s="3" t="s">
         <v>17</v>
       </c>
@@ -7513,7 +7681,9 @@
       <c r="F82" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H82" s="3" t="s">
         <v>17</v>
       </c>
@@ -7538,7 +7708,9 @@
       <c r="F83" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G83" s="3"/>
+      <c r="G83" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H83" s="3" t="s">
         <v>17</v>
       </c>
@@ -7563,7 +7735,9 @@
       <c r="F84" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G84" s="3"/>
+      <c r="G84" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H84" s="3" t="s">
         <v>17</v>
       </c>
@@ -7588,7 +7762,9 @@
       <c r="F85" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="G85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H85" s="3" t="s">
         <v>17</v>
       </c>
@@ -7613,7 +7789,9 @@
       <c r="F86" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="G86" s="3"/>
+      <c r="G86" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H86" s="3" t="s">
         <v>17</v>
       </c>
@@ -7638,7 +7816,9 @@
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H87" s="3" t="s">
         <v>17</v>
       </c>
@@ -7663,7 +7843,9 @@
       <c r="F88" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G88" s="3"/>
+      <c r="G88" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H88" s="3" t="s">
         <v>17</v>
       </c>
@@ -7688,7 +7870,9 @@
       <c r="F89" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G89" s="3"/>
+      <c r="G89" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H89" s="3" t="s">
         <v>17</v>
       </c>
@@ -7713,7 +7897,9 @@
       <c r="F90" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G90" s="3"/>
+      <c r="G90" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H90" s="3" t="s">
         <v>17</v>
       </c>
@@ -7738,7 +7924,9 @@
       <c r="F91" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G91" s="3"/>
+      <c r="G91" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H91" s="3" t="s">
         <v>17</v>
       </c>
@@ -7763,7 +7951,9 @@
       <c r="F92" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H92" s="3" t="s">
         <v>17</v>
       </c>
@@ -7788,7 +7978,9 @@
       <c r="F93" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H93" s="3" t="s">
         <v>17</v>
       </c>
@@ -7813,7 +8005,9 @@
       <c r="F94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H94" s="3" t="s">
         <v>17</v>
       </c>
@@ -7838,7 +8032,9 @@
       <c r="F95" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H95" s="3" t="s">
         <v>17</v>
       </c>
@@ -7863,7 +8059,9 @@
       <c r="F96" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H96" s="3" t="s">
         <v>17</v>
       </c>
@@ -7888,7 +8086,9 @@
       <c r="F97" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="G97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H97" s="3" t="s">
         <v>17</v>
       </c>
@@ -7913,7 +8113,9 @@
       <c r="F98" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="G98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H98" s="3" t="s">
         <v>17</v>
       </c>
@@ -7938,7 +8140,9 @@
       <c r="F99" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H99" s="3" t="s">
         <v>17</v>
       </c>
@@ -7963,7 +8167,9 @@
       <c r="F100" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="G100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H100" s="3" t="s">
         <v>17</v>
       </c>
@@ -7988,7 +8194,9 @@
       <c r="F101" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H101" s="3" t="s">
         <v>17</v>
       </c>
@@ -8013,7 +8221,9 @@
       <c r="F102" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="G102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H102" s="3" t="s">
         <v>17</v>
       </c>
@@ -8038,7 +8248,9 @@
       <c r="F103" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H103" s="3" t="s">
         <v>17</v>
       </c>
@@ -8063,7 +8275,9 @@
       <c r="F104" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="G104" s="3"/>
+      <c r="G104" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H104" s="3" t="s">
         <v>17</v>
       </c>
@@ -8088,7 +8302,9 @@
       <c r="F105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G105" s="3"/>
+      <c r="G105" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H105" s="3" t="s">
         <v>17</v>
       </c>
@@ -8113,7 +8329,9 @@
       <c r="F106" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G106" s="3"/>
+      <c r="G106" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H106" s="3" t="s">
         <v>17</v>
       </c>
@@ -8136,7 +8354,9 @@
         <v>278</v>
       </c>
       <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
+      <c r="G107" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H107" s="3" t="s">
         <v>17</v>
       </c>
@@ -8161,7 +8381,9 @@
       <c r="F108" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G108" s="3"/>
+      <c r="G108" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H108" s="3" t="s">
         <v>17</v>
       </c>
@@ -8186,7 +8408,9 @@
       <c r="F109" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G109" s="3"/>
+      <c r="G109" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H109" s="3" t="s">
         <v>17</v>
       </c>
@@ -8211,7 +8435,9 @@
       <c r="F110" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H110" s="3" t="s">
         <v>17</v>
       </c>
@@ -8236,7 +8462,9 @@
       <c r="F111" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H111" s="3" t="s">
         <v>17</v>
       </c>
@@ -8261,7 +8489,9 @@
       <c r="F112" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H112" s="3" t="s">
         <v>17</v>
       </c>
@@ -8286,7 +8516,9 @@
       <c r="F113" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G113" s="3"/>
+      <c r="G113" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H113" s="3" t="s">
         <v>17</v>
       </c>
@@ -8313,7 +8545,9 @@
       <c r="F114" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H114" s="3" t="s">
         <v>17</v>
       </c>
@@ -8340,7 +8574,9 @@
       <c r="F115" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G115" s="3"/>
+      <c r="G115" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H115" s="3" t="s">
         <v>17</v>
       </c>
@@ -8367,7 +8603,9 @@
       <c r="F116" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G116" s="3"/>
+      <c r="G116" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H116" s="3" t="s">
         <v>17</v>
       </c>
@@ -8392,7 +8630,9 @@
       <c r="F117" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="G117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H117" s="3" t="s">
         <v>17</v>
       </c>
@@ -8417,7 +8657,9 @@
       <c r="F118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H118" s="3" t="s">
         <v>17</v>
       </c>
@@ -8442,7 +8684,9 @@
       <c r="F119" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G119" s="3"/>
+      <c r="G119" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H119" s="3" t="s">
         <v>17</v>
       </c>
@@ -8467,7 +8711,9 @@
       <c r="F120" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G120" s="3"/>
+      <c r="G120" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H120" s="3" t="s">
         <v>17</v>
       </c>
@@ -8492,7 +8738,9 @@
       <c r="F121" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G121" s="3"/>
+      <c r="G121" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H121" s="3" t="s">
         <v>17</v>
       </c>
@@ -8517,7 +8765,9 @@
       <c r="F122" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G122" s="3"/>
+      <c r="G122" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H122" s="3" t="s">
         <v>17</v>
       </c>
@@ -8542,7 +8792,9 @@
       <c r="F123" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G123" s="3"/>
+      <c r="G123" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H123" s="3" t="s">
         <v>17</v>
       </c>
@@ -8567,7 +8819,9 @@
       <c r="F124" s="3">
         <v>1500</v>
       </c>
-      <c r="G124" s="3"/>
+      <c r="G124" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H124" s="3" t="s">
         <v>17</v>
       </c>
@@ -8592,7 +8846,9 @@
       <c r="F125" s="3">
         <v>600</v>
       </c>
-      <c r="G125" s="3"/>
+      <c r="G125" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H125" s="3" t="s">
         <v>17</v>
       </c>
@@ -8617,7 +8873,9 @@
       <c r="F126" s="3">
         <v>2000</v>
       </c>
-      <c r="G126" s="3"/>
+      <c r="G126" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H126" s="3" t="s">
         <v>17</v>
       </c>
@@ -8642,7 +8900,9 @@
       <c r="F127" s="3">
         <v>3000</v>
       </c>
-      <c r="G127" s="3"/>
+      <c r="G127" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H127" s="3" t="s">
         <v>17</v>
       </c>
@@ -8667,7 +8927,9 @@
       <c r="F128" s="3">
         <v>400</v>
       </c>
-      <c r="G128" s="3"/>
+      <c r="G128" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H128" s="3" t="s">
         <v>17</v>
       </c>
@@ -8692,7 +8954,9 @@
       <c r="F129" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G129" s="3"/>
+      <c r="G129" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H129" s="3" t="s">
         <v>17</v>
       </c>
@@ -8717,7 +8981,9 @@
       <c r="F130" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="G130" s="3"/>
+      <c r="G130" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H130" s="3" t="s">
         <v>17</v>
       </c>
@@ -8742,7 +9008,9 @@
       <c r="F131" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G131" s="3"/>
+      <c r="G131" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H131" s="3" t="s">
         <v>17</v>
       </c>
@@ -8767,7 +9035,9 @@
       <c r="F132" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="G132" s="3"/>
+      <c r="G132" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H132" s="3" t="s">
         <v>17</v>
       </c>
@@ -8792,7 +9062,9 @@
       <c r="F133" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="G133" s="3"/>
+      <c r="G133" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H133" s="3" t="s">
         <v>17</v>
       </c>
@@ -8817,7 +9089,9 @@
       <c r="F134" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="G134" s="3"/>
+      <c r="G134" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H134" s="3" t="s">
         <v>17</v>
       </c>
@@ -8842,7 +9116,9 @@
       <c r="F135" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="G135" s="3"/>
+      <c r="G135" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H135" s="3" t="s">
         <v>17</v>
       </c>
@@ -8867,7 +9143,9 @@
       <c r="F136" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="G136" s="3"/>
+      <c r="G136" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H136" s="3" t="s">
         <v>17</v>
       </c>
@@ -8892,7 +9170,9 @@
       <c r="F137" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G137" s="3"/>
+      <c r="G137" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H137" s="3" t="s">
         <v>17</v>
       </c>
@@ -8917,7 +9197,9 @@
       <c r="F138" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G138" s="3"/>
+      <c r="G138" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H138" s="3" t="s">
         <v>17</v>
       </c>
@@ -8942,7 +9224,9 @@
       <c r="F139" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="G139" s="3"/>
+      <c r="G139" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H139" s="3" t="s">
         <v>17</v>
       </c>
@@ -8967,7 +9251,9 @@
       <c r="F140" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G140" s="3"/>
+      <c r="G140" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H140" s="3" t="s">
         <v>17</v>
       </c>
@@ -8992,7 +9278,9 @@
       <c r="F141" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G141" s="3"/>
+      <c r="G141" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H141" s="3" t="s">
         <v>17</v>
       </c>
@@ -9017,7 +9305,9 @@
       <c r="F142" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="G142" s="3"/>
+      <c r="G142" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H142" s="3" t="s">
         <v>17</v>
       </c>
@@ -9042,7 +9332,9 @@
       <c r="F143" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G143" s="3"/>
+      <c r="G143" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H143" s="3" t="s">
         <v>17</v>
       </c>
@@ -9067,7 +9359,9 @@
       <c r="F144" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G144" s="3"/>
+      <c r="G144" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H144" s="3" t="s">
         <v>17</v>
       </c>
@@ -9092,7 +9386,9 @@
       <c r="F145" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="G145" s="3"/>
+      <c r="G145" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H145" s="3" t="s">
         <v>17</v>
       </c>
@@ -9117,7 +9413,9 @@
       <c r="F146" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G146" s="3"/>
+      <c r="G146" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H146" s="3" t="s">
         <v>17</v>
       </c>
@@ -9142,7 +9440,9 @@
       <c r="F147" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G147" s="3"/>
+      <c r="G147" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H147" s="3" t="s">
         <v>17</v>
       </c>
@@ -9167,7 +9467,9 @@
       <c r="F148" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="G148" s="3"/>
+      <c r="G148" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H148" s="3" t="s">
         <v>17</v>
       </c>
@@ -9192,7 +9494,9 @@
       <c r="F149" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G149" s="3"/>
+      <c r="G149" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H149" s="3" t="s">
         <v>17</v>
       </c>
@@ -9217,7 +9521,9 @@
       <c r="F150" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G150" s="3"/>
+      <c r="G150" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H150" s="3" t="s">
         <v>17</v>
       </c>
@@ -9242,7 +9548,9 @@
       <c r="F151" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="G151" s="3"/>
+      <c r="G151" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H151" s="3" t="s">
         <v>17</v>
       </c>
@@ -9267,7 +9575,9 @@
       <c r="F152" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G152" s="3"/>
+      <c r="G152" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H152" s="3" t="s">
         <v>17</v>
       </c>
@@ -9292,7 +9602,9 @@
       <c r="F153" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G153" s="3"/>
+      <c r="G153" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H153" s="3" t="s">
         <v>17</v>
       </c>
@@ -9317,7 +9629,9 @@
       <c r="F154" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G154" s="3"/>
+      <c r="G154" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H154" s="3" t="s">
         <v>17</v>
       </c>
@@ -9342,7 +9656,9 @@
       <c r="F155" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G155" s="3"/>
+      <c r="G155" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H155" s="3" t="s">
         <v>17</v>
       </c>
@@ -9367,7 +9683,9 @@
       <c r="F156" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G156" s="3"/>
+      <c r="G156" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H156" s="3" t="s">
         <v>17</v>
       </c>
@@ -9392,7 +9710,9 @@
       <c r="F157" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G157" s="3"/>
+      <c r="G157" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H157" s="3" t="s">
         <v>17</v>
       </c>
@@ -9417,7 +9737,9 @@
       <c r="F158" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G158" s="3"/>
+      <c r="G158" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H158" s="3" t="s">
         <v>17</v>
       </c>
@@ -9442,7 +9764,9 @@
       <c r="F159" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G159" s="3"/>
+      <c r="G159" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H159" s="3" t="s">
         <v>17</v>
       </c>
@@ -9467,7 +9791,9 @@
       <c r="F160" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G160" s="3"/>
+      <c r="G160" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H160" s="3" t="s">
         <v>17</v>
       </c>
@@ -9492,7 +9818,9 @@
       <c r="F161" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G161" s="3"/>
+      <c r="G161" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H161" s="3" t="s">
         <v>17</v>
       </c>
@@ -9517,7 +9845,9 @@
       <c r="F162" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G162" s="3"/>
+      <c r="G162" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H162" s="3" t="s">
         <v>17</v>
       </c>
@@ -9542,7 +9872,9 @@
       <c r="F163" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G163" s="3"/>
+      <c r="G163" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H163" s="3" t="s">
         <v>17</v>
       </c>
@@ -9567,7 +9899,9 @@
       <c r="F164" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G164" s="3"/>
+      <c r="G164" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H164" s="3" t="s">
         <v>17</v>
       </c>
@@ -9592,7 +9926,9 @@
       <c r="F165" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G165" s="3"/>
+      <c r="G165" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H165" s="3" t="s">
         <v>17</v>
       </c>
@@ -9617,7 +9953,9 @@
       <c r="F166" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G166" s="3"/>
+      <c r="G166" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H166" s="3" t="s">
         <v>17</v>
       </c>
@@ -9642,7 +9980,9 @@
       <c r="F167" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G167" s="3"/>
+      <c r="G167" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H167" s="3" t="s">
         <v>17</v>
       </c>
@@ -9667,7 +10007,9 @@
       <c r="F168" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G168" s="3"/>
+      <c r="G168" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H168" s="3" t="s">
         <v>17</v>
       </c>
@@ -9692,7 +10034,9 @@
       <c r="F169" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G169" s="3"/>
+      <c r="G169" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H169" s="3" t="s">
         <v>17</v>
       </c>
@@ -9717,7 +10061,9 @@
       <c r="F170" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G170" s="3"/>
+      <c r="G170" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H170" s="3" t="s">
         <v>17</v>
       </c>
@@ -9742,7 +10088,9 @@
       <c r="F171" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G171" s="3"/>
+      <c r="G171" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H171" s="3" t="s">
         <v>17</v>
       </c>
@@ -9767,7 +10115,9 @@
       <c r="F172" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G172" s="3"/>
+      <c r="G172" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H172" s="3" t="s">
         <v>17</v>
       </c>
@@ -9792,7 +10142,9 @@
       <c r="F173" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G173" s="3"/>
+      <c r="G173" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H173" s="3" t="s">
         <v>17</v>
       </c>
@@ -9817,7 +10169,9 @@
       <c r="F174" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="G174" s="3"/>
+      <c r="G174" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H174" s="3" t="s">
         <v>17</v>
       </c>
@@ -9842,7 +10196,9 @@
       <c r="F175" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G175" s="3"/>
+      <c r="G175" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H175" s="3" t="s">
         <v>17</v>
       </c>
@@ -9867,7 +10223,9 @@
       <c r="F176" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="G176" s="3"/>
+      <c r="G176" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H176" s="3" t="s">
         <v>17</v>
       </c>
@@ -9892,7 +10250,9 @@
       <c r="F177" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G177" s="3"/>
+      <c r="G177" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H177" s="3" t="s">
         <v>17</v>
       </c>
@@ -9917,7 +10277,9 @@
       <c r="F178" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G178" s="3"/>
+      <c r="G178" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H178" s="3" t="s">
         <v>17</v>
       </c>
@@ -9942,7 +10304,9 @@
       <c r="F179" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G179" s="3"/>
+      <c r="G179" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H179" s="3" t="s">
         <v>17</v>
       </c>
@@ -9967,7 +10331,9 @@
       <c r="F180" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G180" s="3"/>
+      <c r="G180" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H180" s="3" t="s">
         <v>17</v>
       </c>
@@ -9992,7 +10358,9 @@
       <c r="F181" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="G181" s="3"/>
+      <c r="G181" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H181" s="3" t="s">
         <v>17</v>
       </c>
@@ -10017,7 +10385,9 @@
       <c r="F182" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="G182" s="3"/>
+      <c r="G182" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H182" s="3" t="s">
         <v>17</v>
       </c>
@@ -10042,7 +10412,9 @@
       <c r="F183" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G183" s="3"/>
+      <c r="G183" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H183" s="3" t="s">
         <v>17</v>
       </c>
@@ -10067,7 +10439,9 @@
       <c r="F184" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G184" s="3"/>
+      <c r="G184" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H184" s="3" t="s">
         <v>17</v>
       </c>
@@ -10092,7 +10466,9 @@
       <c r="F185" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G185" s="3"/>
+      <c r="G185" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H185" s="3" t="s">
         <v>17</v>
       </c>
@@ -10117,7 +10493,9 @@
       <c r="F186" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="G186" s="3"/>
+      <c r="G186" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H186" s="3" t="s">
         <v>17</v>
       </c>
@@ -10142,7 +10520,9 @@
       <c r="F187" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G187" s="3"/>
+      <c r="G187" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H187" s="3" t="s">
         <v>17</v>
       </c>
@@ -10167,7 +10547,9 @@
       <c r="F188" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G188" s="3"/>
+      <c r="G188" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H188" s="3" t="s">
         <v>17</v>
       </c>
@@ -10192,7 +10574,9 @@
       <c r="F189" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G189" s="3"/>
+      <c r="G189" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H189" s="3" t="s">
         <v>17</v>
       </c>
@@ -10217,7 +10601,9 @@
       <c r="F190" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="G190" s="3"/>
+      <c r="G190" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H190" s="3" t="s">
         <v>17</v>
       </c>
@@ -10242,7 +10628,9 @@
       <c r="F191" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="G191" s="3"/>
+      <c r="G191" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H191" s="3" t="s">
         <v>17</v>
       </c>
@@ -10267,7 +10655,9 @@
       <c r="F192" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="G192" s="3"/>
+      <c r="G192" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H192" s="3" t="s">
         <v>17</v>
       </c>
@@ -10292,7 +10682,9 @@
       <c r="F193" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="G193" s="3"/>
+      <c r="G193" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H193" s="3" t="s">
         <v>17</v>
       </c>
@@ -10317,7 +10709,9 @@
       <c r="F194" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G194" s="3"/>
+      <c r="G194" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H194" s="3" t="s">
         <v>17</v>
       </c>
@@ -10342,7 +10736,9 @@
       <c r="F195" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G195" s="3"/>
+      <c r="G195" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H195" s="3" t="s">
         <v>17</v>
       </c>
@@ -10367,7 +10763,9 @@
       <c r="F196" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G196" s="3"/>
+      <c r="G196" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H196" s="3" t="s">
         <v>17</v>
       </c>
@@ -10392,7 +10790,9 @@
       <c r="F197" s="3">
         <v>34</v>
       </c>
-      <c r="G197" s="3"/>
+      <c r="G197" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H197" s="3" t="s">
         <v>17</v>
       </c>
@@ -10417,7 +10817,9 @@
       <c r="F198" s="3">
         <v>34</v>
       </c>
-      <c r="G198" s="3"/>
+      <c r="G198" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H198" s="3" t="s">
         <v>17</v>
       </c>
@@ -10442,7 +10844,9 @@
       <c r="F199" s="3">
         <v>12</v>
       </c>
-      <c r="G199" s="3"/>
+      <c r="G199" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H199" s="3" t="s">
         <v>17</v>
       </c>
@@ -10467,7 +10871,9 @@
       <c r="F200" s="3">
         <v>12</v>
       </c>
-      <c r="G200" s="3"/>
+      <c r="G200" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H200" s="3" t="s">
         <v>17</v>
       </c>
@@ -10492,7 +10898,9 @@
       <c r="F201" s="3">
         <v>46</v>
       </c>
-      <c r="G201" s="3"/>
+      <c r="G201" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H201" s="3" t="s">
         <v>17</v>
       </c>
@@ -10517,7 +10925,9 @@
       <c r="F202" s="3">
         <v>32</v>
       </c>
-      <c r="G202" s="3"/>
+      <c r="G202" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H202" s="3" t="s">
         <v>17</v>
       </c>
@@ -10542,7 +10952,9 @@
       <c r="F203" s="3">
         <v>40</v>
       </c>
-      <c r="G203" s="3"/>
+      <c r="G203" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H203" s="3" t="s">
         <v>17</v>
       </c>
@@ -10567,7 +10979,9 @@
       <c r="F204" s="3">
         <v>30</v>
       </c>
-      <c r="G204" s="3"/>
+      <c r="G204" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H204" s="3" t="s">
         <v>17</v>
       </c>
@@ -10592,7 +11006,9 @@
       <c r="F205" s="3">
         <v>26</v>
       </c>
-      <c r="G205" s="3"/>
+      <c r="G205" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H205" s="3" t="s">
         <v>17</v>
       </c>
@@ -10617,7 +11033,9 @@
       <c r="F206" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G206" s="3"/>
+      <c r="G206" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H206" s="3" t="s">
         <v>17</v>
       </c>
@@ -10642,7 +11060,9 @@
       <c r="F207" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="G207" s="3"/>
+      <c r="G207" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H207" s="3" t="s">
         <v>17</v>
       </c>
@@ -10667,7 +11087,9 @@
       <c r="F208" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="G208" s="3"/>
+      <c r="G208" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H208" s="3" t="s">
         <v>17</v>
       </c>
@@ -10692,7 +11114,9 @@
       <c r="F209" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="G209" s="3"/>
+      <c r="G209" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H209" s="3" t="s">
         <v>17</v>
       </c>
@@ -10717,7 +11141,9 @@
       <c r="F210" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G210" s="3"/>
+      <c r="G210" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H210" s="3" t="s">
         <v>17</v>
       </c>
@@ -10742,7 +11168,9 @@
       <c r="F211" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G211" s="3"/>
+      <c r="G211" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H211" s="3" t="s">
         <v>17</v>
       </c>
@@ -10767,7 +11195,9 @@
       <c r="F212" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="G212" s="3"/>
+      <c r="G212" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H212" s="3" t="s">
         <v>17</v>
       </c>
@@ -10792,7 +11222,9 @@
       <c r="F213" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G213" s="3"/>
+      <c r="G213" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H213" s="3" t="s">
         <v>17</v>
       </c>
@@ -10817,7 +11249,9 @@
       <c r="F214" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="G214" s="3"/>
+      <c r="G214" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H214" s="3" t="s">
         <v>17</v>
       </c>
@@ -10842,7 +11276,9 @@
       <c r="F215" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="G215" s="3"/>
+      <c r="G215" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H215" s="3" t="s">
         <v>17</v>
       </c>
@@ -10867,7 +11303,9 @@
       <c r="F216" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G216" s="3"/>
+      <c r="G216" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H216" s="3" t="s">
         <v>17</v>
       </c>
@@ -10892,7 +11330,9 @@
       <c r="F217" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G217" s="3"/>
+      <c r="G217" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H217" s="3" t="s">
         <v>17</v>
       </c>
@@ -10917,7 +11357,9 @@
       <c r="F218" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G218" s="3"/>
+      <c r="G218" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H218" s="3" t="s">
         <v>17</v>
       </c>
@@ -10942,7 +11384,9 @@
       <c r="F219" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G219" s="3"/>
+      <c r="G219" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H219" s="3" t="s">
         <v>17</v>
       </c>
@@ -10967,7 +11411,9 @@
       <c r="F220" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="G220" s="3"/>
+      <c r="G220" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H220" s="3" t="s">
         <v>17</v>
       </c>
@@ -10992,7 +11438,9 @@
       <c r="F221" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="G221" s="3"/>
+      <c r="G221" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H221" s="3" t="s">
         <v>17</v>
       </c>
@@ -11015,7 +11463,9 @@
         <v>306</v>
       </c>
       <c r="F222" s="3"/>
-      <c r="G222" s="3"/>
+      <c r="G222" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H222" s="3" t="s">
         <v>17</v>
       </c>
@@ -11040,7 +11490,9 @@
       <c r="F223" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="G223" s="3"/>
+      <c r="G223" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H223" s="3" t="s">
         <v>17</v>
       </c>
@@ -11063,7 +11515,9 @@
         <v>309</v>
       </c>
       <c r="F224" s="3"/>
-      <c r="G224" s="3"/>
+      <c r="G224" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H224" s="3" t="s">
         <v>17</v>
       </c>
@@ -11088,7 +11542,9 @@
       <c r="F225" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G225" s="3"/>
+      <c r="G225" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H225" s="3" t="s">
         <v>17</v>
       </c>
@@ -11113,7 +11569,9 @@
       <c r="F226" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G226" s="3"/>
+      <c r="G226" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H226" s="3" t="s">
         <v>17</v>
       </c>
@@ -11138,7 +11596,9 @@
       <c r="F227" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G227" s="3"/>
+      <c r="G227" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H227" s="3" t="s">
         <v>17</v>
       </c>
@@ -11163,7 +11623,9 @@
       <c r="F228" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G228" s="3"/>
+      <c r="G228" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H228" s="3" t="s">
         <v>17</v>
       </c>
@@ -11188,7 +11650,9 @@
       <c r="F229" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G229" s="3"/>
+      <c r="G229" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H229" s="3" t="s">
         <v>17</v>
       </c>
@@ -11213,7 +11677,9 @@
       <c r="F230" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G230" s="3"/>
+      <c r="G230" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H230" s="3" t="s">
         <v>17</v>
       </c>
@@ -11238,7 +11704,9 @@
       <c r="F231" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G231" s="3"/>
+      <c r="G231" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H231" s="3" t="s">
         <v>17</v>
       </c>
@@ -11263,7 +11731,9 @@
       <c r="F232" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G232" s="3"/>
+      <c r="G232" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H232" s="3" t="s">
         <v>17</v>
       </c>
@@ -11288,7 +11758,9 @@
       <c r="F233" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G233" s="3"/>
+      <c r="G233" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H233" s="3" t="s">
         <v>17</v>
       </c>
@@ -11313,7 +11785,9 @@
       <c r="F234" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="G234" s="3"/>
+      <c r="G234" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H234" s="3" t="s">
         <v>17</v>
       </c>
@@ -11338,7 +11812,9 @@
       <c r="F235" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G235" s="3"/>
+      <c r="G235" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H235" s="3" t="s">
         <v>17</v>
       </c>
@@ -11363,7 +11839,9 @@
       <c r="F236" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="G236" s="3"/>
+      <c r="G236" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H236" s="3" t="s">
         <v>17</v>
       </c>
@@ -11390,7 +11868,9 @@
       <c r="F237" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G237" s="3"/>
+      <c r="G237" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H237" s="3" t="s">
         <v>17</v>
       </c>
@@ -11415,7 +11895,9 @@
       <c r="F238" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G238" s="3"/>
+      <c r="G238" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H238" s="3" t="s">
         <v>17</v>
       </c>
@@ -11440,7 +11922,9 @@
       <c r="F239" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G239" s="3"/>
+      <c r="G239" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H239" s="3" t="s">
         <v>17</v>
       </c>
@@ -11465,7 +11949,9 @@
       <c r="F240" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G240" s="3"/>
+      <c r="G240" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H240" s="3" t="s">
         <v>17</v>
       </c>
@@ -11490,7 +11976,9 @@
       <c r="F241" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G241" s="3"/>
+      <c r="G241" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H241" s="3" t="s">
         <v>17</v>
       </c>
@@ -11515,7 +12003,9 @@
       <c r="F242" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G242" s="3"/>
+      <c r="G242" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H242" s="3" t="s">
         <v>17</v>
       </c>
@@ -11540,7 +12030,9 @@
       <c r="F243" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G243" s="3"/>
+      <c r="G243" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H243" s="3" t="s">
         <v>17</v>
       </c>
@@ -11565,7 +12057,9 @@
       <c r="F244" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G244" s="3"/>
+      <c r="G244" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H244" s="3" t="s">
         <v>17</v>
       </c>
@@ -11590,7 +12084,9 @@
       <c r="F245" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G245" s="3"/>
+      <c r="G245" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H245" s="3" t="s">
         <v>17</v>
       </c>
@@ -11615,7 +12111,9 @@
       <c r="F246" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G246" s="3"/>
+      <c r="G246" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H246" s="3" t="s">
         <v>17</v>
       </c>
@@ -11640,7 +12138,9 @@
       <c r="F247" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G247" s="3"/>
+      <c r="G247" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H247" s="3" t="s">
         <v>17</v>
       </c>
@@ -11665,7 +12165,9 @@
       <c r="F248" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G248" s="3"/>
+      <c r="G248" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H248" s="3" t="s">
         <v>17</v>
       </c>
@@ -11690,7 +12192,9 @@
       <c r="F249" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G249" s="3"/>
+      <c r="G249" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H249" s="3" t="s">
         <v>17</v>
       </c>
@@ -11715,7 +12219,9 @@
       <c r="F250" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G250" s="3"/>
+      <c r="G250" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H250" s="3" t="s">
         <v>17</v>
       </c>
@@ -11740,7 +12246,9 @@
       <c r="F251" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G251" s="3"/>
+      <c r="G251" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H251" s="3" t="s">
         <v>17</v>
       </c>
@@ -11765,7 +12273,9 @@
       <c r="F252" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G252" s="3"/>
+      <c r="G252" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H252" s="3" t="s">
         <v>17</v>
       </c>
@@ -11790,7 +12300,9 @@
       <c r="F253" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G253" s="3"/>
+      <c r="G253" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H253" s="3" t="s">
         <v>17</v>
       </c>
@@ -11815,7 +12327,9 @@
       <c r="F254" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G254" s="3"/>
+      <c r="G254" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H254" s="3" t="s">
         <v>17</v>
       </c>
@@ -11840,7 +12354,9 @@
       <c r="F255" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G255" s="3"/>
+      <c r="G255" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H255" s="3" t="s">
         <v>17</v>
       </c>
@@ -11865,7 +12381,9 @@
       <c r="F256" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G256" s="3"/>
+      <c r="G256" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H256" s="3" t="s">
         <v>17</v>
       </c>
@@ -11890,7 +12408,9 @@
       <c r="F257" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G257" s="3"/>
+      <c r="G257" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H257" s="3" t="s">
         <v>17</v>
       </c>
@@ -11915,7 +12435,9 @@
       <c r="F258" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G258" s="3"/>
+      <c r="G258" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="H258" s="3" t="s">
         <v>17</v>
       </c>
@@ -12030,96 +12552,112 @@
       <c r="I262" s="3"/>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A263" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B263" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D263" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="E263" s="3"/>
-      <c r="F263" s="3"/>
-      <c r="G263" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="H263" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I263" s="3"/>
+      <c r="A263" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="B263" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="C263" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="D263" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E263" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F263" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G263" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="H263" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I263" s="10"/>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A264" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B264" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D264" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="E264" s="3"/>
-      <c r="F264" s="3"/>
-      <c r="G264" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="H264" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I264" s="3"/>
+      <c r="A264" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="C264" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="D264" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E264" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F264" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G264" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="H264" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I264" s="10"/>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A265" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="B265" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="C265" s="10"/>
-      <c r="D265" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E265" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="F265" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="G265" s="10"/>
-      <c r="H265" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I265" s="10"/>
+      <c r="A265" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="D265" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="E265" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F265" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="G265" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="H265" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I265" s="9"/>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A266" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="B266" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="C266" s="10"/>
-      <c r="D266" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E266" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="F266" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="G266" s="10"/>
-      <c r="H266" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I266" s="10"/>
+      <c r="A266" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="D266" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E266" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F266" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="G266" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="H266" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I266" s="9"/>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="9" t="s">
@@ -12132,7 +12670,7 @@
         <v>497</v>
       </c>
       <c r="D267" s="9" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E267" s="9" t="s">
         <v>355</v>
@@ -12159,7 +12697,7 @@
         <v>497</v>
       </c>
       <c r="D268" s="9" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E268" s="9" t="s">
         <v>355</v>
@@ -12186,13 +12724,13 @@
         <v>497</v>
       </c>
       <c r="D269" s="9" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E269" s="9" t="s">
         <v>355</v>
       </c>
       <c r="F269" s="9" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="G269" s="9" t="s">
         <v>485</v>
@@ -12213,13 +12751,13 @@
         <v>497</v>
       </c>
       <c r="D270" s="9" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E270" s="9" t="s">
         <v>355</v>
       </c>
       <c r="F270" s="9" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="G270" s="9" t="s">
         <v>485</v>
@@ -12240,13 +12778,13 @@
         <v>497</v>
       </c>
       <c r="D271" s="9" t="s">
-        <v>464</v>
+        <v>135</v>
       </c>
       <c r="E271" s="9" t="s">
-        <v>355</v>
+        <v>136</v>
       </c>
       <c r="F271" s="9" t="s">
-        <v>466</v>
+        <v>394</v>
       </c>
       <c r="G271" s="9" t="s">
         <v>485</v>
@@ -12267,13 +12805,13 @@
         <v>497</v>
       </c>
       <c r="D272" s="9" t="s">
-        <v>465</v>
+        <v>135</v>
       </c>
       <c r="E272" s="9" t="s">
-        <v>355</v>
+        <v>137</v>
       </c>
       <c r="F272" s="9" t="s">
-        <v>466</v>
+        <v>138</v>
       </c>
       <c r="G272" s="9" t="s">
         <v>485</v>
@@ -12294,13 +12832,13 @@
         <v>497</v>
       </c>
       <c r="D273" s="9" t="s">
-        <v>135</v>
+        <v>525</v>
       </c>
       <c r="E273" s="9" t="s">
-        <v>136</v>
+        <v>526</v>
       </c>
       <c r="F273" s="9" t="s">
-        <v>394</v>
+        <v>38</v>
       </c>
       <c r="G273" s="9" t="s">
         <v>485</v>
@@ -12321,13 +12859,13 @@
         <v>497</v>
       </c>
       <c r="D274" s="9" t="s">
-        <v>135</v>
+        <v>498</v>
       </c>
       <c r="E274" s="9" t="s">
-        <v>137</v>
+        <v>499</v>
       </c>
       <c r="F274" s="9" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="G274" s="9" t="s">
         <v>485</v>
@@ -12348,13 +12886,13 @@
         <v>497</v>
       </c>
       <c r="D275" s="9" t="s">
-        <v>525</v>
+        <v>498</v>
       </c>
       <c r="E275" s="9" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F275" s="9" t="s">
-        <v>38</v>
+        <v>524</v>
       </c>
       <c r="G275" s="9" t="s">
         <v>485</v>
@@ -12378,10 +12916,10 @@
         <v>498</v>
       </c>
       <c r="E276" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F276" s="9" t="s">
-        <v>18</v>
+        <v>501</v>
       </c>
       <c r="G276" s="9" t="s">
         <v>485</v>
@@ -12402,13 +12940,13 @@
         <v>497</v>
       </c>
       <c r="D277" s="9" t="s">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="E277" s="9" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
       <c r="F277" s="9" t="s">
-        <v>524</v>
+        <v>18</v>
       </c>
       <c r="G277" s="9" t="s">
         <v>485</v>
@@ -12429,13 +12967,13 @@
         <v>497</v>
       </c>
       <c r="D278" s="9" t="s">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="E278" s="9" t="s">
-        <v>500</v>
+        <v>523</v>
       </c>
       <c r="F278" s="9" t="s">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="G278" s="9" t="s">
         <v>485</v>
@@ -12459,10 +12997,10 @@
         <v>522</v>
       </c>
       <c r="E279" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F279" s="9" t="s">
-        <v>18</v>
+        <v>501</v>
       </c>
       <c r="G279" s="9" t="s">
         <v>485</v>
@@ -12483,13 +13021,13 @@
         <v>497</v>
       </c>
       <c r="D280" s="9" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="E280" s="9" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="F280" s="9" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="G280" s="9" t="s">
         <v>485</v>
@@ -12510,13 +13048,13 @@
         <v>497</v>
       </c>
       <c r="D281" s="9" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="E281" s="9" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F281" s="9" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G281" s="9" t="s">
         <v>485</v>
@@ -12540,10 +13078,10 @@
         <v>502</v>
       </c>
       <c r="E282" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="F282" s="9" t="s">
-        <v>504</v>
+        <v>506</v>
+      </c>
+      <c r="F282" s="9">
+        <v>600</v>
       </c>
       <c r="G282" s="9" t="s">
         <v>485</v>
@@ -12567,10 +13105,10 @@
         <v>502</v>
       </c>
       <c r="E283" s="9" t="s">
-        <v>505</v>
+        <v>279</v>
       </c>
       <c r="F283" s="9" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="G283" s="9" t="s">
         <v>485</v>
@@ -12594,10 +13132,10 @@
         <v>502</v>
       </c>
       <c r="E284" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="F284" s="9">
-        <v>600</v>
+        <v>508</v>
+      </c>
+      <c r="F284" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="G284" s="9" t="s">
         <v>485</v>
@@ -12621,10 +13159,10 @@
         <v>502</v>
       </c>
       <c r="E285" s="9" t="s">
-        <v>279</v>
+        <v>509</v>
       </c>
       <c r="F285" s="9" t="s">
-        <v>507</v>
+        <v>17</v>
       </c>
       <c r="G285" s="9" t="s">
         <v>485</v>
@@ -12645,13 +13183,13 @@
         <v>497</v>
       </c>
       <c r="D286" s="9" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="E286" s="9" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F286" s="9" t="s">
-        <v>18</v>
+        <v>512</v>
       </c>
       <c r="G286" s="9" t="s">
         <v>485</v>
@@ -12672,13 +13210,13 @@
         <v>497</v>
       </c>
       <c r="D287" s="9" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="E287" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="F287" s="9" t="s">
-        <v>17</v>
+        <v>513</v>
+      </c>
+      <c r="F287" s="9">
+        <v>-107</v>
       </c>
       <c r="G287" s="9" t="s">
         <v>485</v>
@@ -12702,10 +13240,10 @@
         <v>510</v>
       </c>
       <c r="E288" s="9" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F288" s="9" t="s">
-        <v>512</v>
+        <v>37</v>
       </c>
       <c r="G288" s="9" t="s">
         <v>485</v>
@@ -12729,10 +13267,10 @@
         <v>510</v>
       </c>
       <c r="E289" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="F289" s="9">
-        <v>-107</v>
+        <v>515</v>
+      </c>
+      <c r="F289" s="9" t="s">
+        <v>516</v>
       </c>
       <c r="G289" s="9" t="s">
         <v>485</v>
@@ -12753,16 +13291,16 @@
         <v>497</v>
       </c>
       <c r="D290" s="9" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="E290" s="9" t="s">
-        <v>514</v>
+        <v>42</v>
       </c>
       <c r="F290" s="9" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G290" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H290" s="9" t="s">
         <v>17</v>
@@ -12780,16 +13318,16 @@
         <v>497</v>
       </c>
       <c r="D291" s="9" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="E291" s="9" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F291" s="9" t="s">
-        <v>516</v>
+        <v>72</v>
       </c>
       <c r="G291" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H291" s="9" t="s">
         <v>17</v>
@@ -12810,10 +13348,10 @@
         <v>517</v>
       </c>
       <c r="E292" s="9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F292" s="9" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="G292" s="9" t="s">
         <v>486</v>
@@ -12837,10 +13375,10 @@
         <v>517</v>
       </c>
       <c r="E293" s="9" t="s">
-        <v>518</v>
+        <v>66</v>
       </c>
       <c r="F293" s="9" t="s">
-        <v>72</v>
+        <v>305</v>
       </c>
       <c r="G293" s="9" t="s">
         <v>486</v>
@@ -12864,10 +13402,10 @@
         <v>517</v>
       </c>
       <c r="E294" s="9" t="s">
-        <v>52</v>
+        <v>519</v>
       </c>
       <c r="F294" s="9" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="G294" s="9" t="s">
         <v>486</v>
@@ -12891,10 +13429,10 @@
         <v>517</v>
       </c>
       <c r="E295" s="9" t="s">
-        <v>66</v>
+        <v>520</v>
       </c>
       <c r="F295" s="9" t="s">
-        <v>305</v>
+        <v>521</v>
       </c>
       <c r="G295" s="9" t="s">
         <v>486</v>
@@ -12903,60 +13441,6 @@
         <v>17</v>
       </c>
       <c r="I295" s="9"/>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A296" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="B296" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="C296" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="D296" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="E296" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="F296" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G296" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="H296" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I296" s="9"/>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A297" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="B297" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="C297" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="D297" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="E297" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="F297" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="G297" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="H297" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I297" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F258" xr:uid="{04129BFA-1C57-4A9F-9E8B-6ECAA0BFBBBF}"/>

--- a/app/gpl_audit/GPL.xlsx
+++ b/app/gpl_audit/GPL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aj_mac/Documents/Atel/server/code/app/gpl_audit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D11152B-4D91-2E4B-BBDA-EA65C391E6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D9F6B3-FDC1-6F49-851C-66F4C357A1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14380" yWindow="640" windowWidth="14420" windowHeight="16120" firstSheet="1" activeTab="5" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16080" firstSheet="1" activeTab="2" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
   </bookViews>
   <sheets>
     <sheet name="TermPointToAmf" sheetId="2" r:id="rId1"/>
@@ -5741,7 +5741,7 @@
         <v>25</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -19699,7 +19699,7 @@
         <v>115</v>
       </c>
       <c r="F487" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G487" s="3" t="s">
         <v>578</v>
